--- a/artfynd/A 37449-2025 artfynd.xlsx
+++ b/artfynd/A 37449-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>84181648</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100761</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536357.2255991686</v>
+        <v>536357</v>
       </c>
       <c r="R2" t="n">
-        <v>6909846.556067738</v>
+        <v>6909847</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,19 +748,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,7 @@
         <v>84181660</v>
       </c>
       <c r="B3" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103086</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536357.2255991686</v>
+        <v>536357</v>
       </c>
       <c r="R3" t="n">
-        <v>6909846.556067738</v>
+        <v>6909847</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,19 +859,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,12 +900,7 @@
         <v>84181640</v>
       </c>
       <c r="B4" t="n">
-        <v>101134</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536376.5629264562</v>
+        <v>536377</v>
       </c>
       <c r="R4" t="n">
-        <v>6909866.758769457</v>
+        <v>6909867</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1005,19 +970,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,12 +1011,7 @@
         <v>84181649</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100668</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536357.2255991686</v>
+        <v>536357</v>
       </c>
       <c r="R5" t="n">
-        <v>6909846.556067738</v>
+        <v>6909847</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1131,19 +1081,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,12 +1122,7 @@
         <v>84181685</v>
       </c>
       <c r="B6" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103086</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536317.6190820948</v>
+        <v>536318</v>
       </c>
       <c r="R6" t="n">
-        <v>6909806.140559386</v>
+        <v>6909806</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1257,19 +1192,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,12 +1233,7 @@
         <v>84181681</v>
       </c>
       <c r="B7" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536357.2255991686</v>
+        <v>536357</v>
       </c>
       <c r="R7" t="n">
-        <v>6909846.556067738</v>
+        <v>6909847</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1383,19 +1303,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,12 +1344,7 @@
         <v>84181705</v>
       </c>
       <c r="B8" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536317.6190820948</v>
+        <v>536318</v>
       </c>
       <c r="R8" t="n">
-        <v>6909806.140559386</v>
+        <v>6909806</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1509,19 +1414,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1560,12 +1455,7 @@
         <v>84181703</v>
       </c>
       <c r="B9" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100761</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536317.6190820948</v>
+        <v>536318</v>
       </c>
       <c r="R9" t="n">
-        <v>6909806.140559386</v>
+        <v>6909806</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1635,19 +1525,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,12 +1566,7 @@
         <v>84181687</v>
       </c>
       <c r="B10" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100668</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536317.6190820948</v>
+        <v>536318</v>
       </c>
       <c r="R10" t="n">
-        <v>6909806.140559386</v>
+        <v>6909806</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1761,19 +1636,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 37449-2025 artfynd.xlsx
+++ b/artfynd/A 37449-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181648</v>
       </c>
       <c r="B2" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181660</v>
       </c>
       <c r="B3" t="n">
-        <v>103086</v>
+        <v>103094</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181640</v>
       </c>
       <c r="B4" t="n">
-        <v>103100</v>
+        <v>103108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181649</v>
       </c>
       <c r="B5" t="n">
-        <v>100668</v>
+        <v>100674</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181685</v>
       </c>
       <c r="B6" t="n">
-        <v>103086</v>
+        <v>103094</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181681</v>
       </c>
       <c r="B7" t="n">
-        <v>98912</v>
+        <v>98918</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181705</v>
       </c>
       <c r="B8" t="n">
-        <v>98912</v>
+        <v>98918</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181703</v>
       </c>
       <c r="B9" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181687</v>
       </c>
       <c r="B10" t="n">
-        <v>100668</v>
+        <v>100674</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37449-2025 artfynd.xlsx
+++ b/artfynd/A 37449-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181648</v>
       </c>
       <c r="B2" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181660</v>
       </c>
       <c r="B3" t="n">
-        <v>103094</v>
+        <v>103106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181640</v>
       </c>
       <c r="B4" t="n">
-        <v>103108</v>
+        <v>103120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181649</v>
       </c>
       <c r="B5" t="n">
-        <v>100674</v>
+        <v>100679</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181685</v>
       </c>
       <c r="B6" t="n">
-        <v>103094</v>
+        <v>103106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181681</v>
       </c>
       <c r="B7" t="n">
-        <v>98918</v>
+        <v>98921</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181705</v>
       </c>
       <c r="B8" t="n">
-        <v>98918</v>
+        <v>98921</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181703</v>
       </c>
       <c r="B9" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181687</v>
       </c>
       <c r="B10" t="n">
-        <v>100674</v>
+        <v>100679</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37449-2025 artfynd.xlsx
+++ b/artfynd/A 37449-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181648</v>
       </c>
       <c r="B2" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181660</v>
       </c>
       <c r="B3" t="n">
-        <v>103106</v>
+        <v>103112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181640</v>
       </c>
       <c r="B4" t="n">
-        <v>103120</v>
+        <v>103126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181649</v>
       </c>
       <c r="B5" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181685</v>
       </c>
       <c r="B6" t="n">
-        <v>103106</v>
+        <v>103112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181681</v>
       </c>
       <c r="B7" t="n">
-        <v>98921</v>
+        <v>98925</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181705</v>
       </c>
       <c r="B8" t="n">
-        <v>98921</v>
+        <v>98925</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181703</v>
       </c>
       <c r="B9" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181687</v>
       </c>
       <c r="B10" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37449-2025 artfynd.xlsx
+++ b/artfynd/A 37449-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181648</v>
       </c>
       <c r="B2" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181660</v>
       </c>
       <c r="B3" t="n">
-        <v>103112</v>
+        <v>103114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181640</v>
       </c>
       <c r="B4" t="n">
-        <v>103126</v>
+        <v>103128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181649</v>
       </c>
       <c r="B5" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181685</v>
       </c>
       <c r="B6" t="n">
-        <v>103112</v>
+        <v>103114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181681</v>
       </c>
       <c r="B7" t="n">
-        <v>98925</v>
+        <v>98926</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181705</v>
       </c>
       <c r="B8" t="n">
-        <v>98925</v>
+        <v>98926</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181703</v>
       </c>
       <c r="B9" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181687</v>
       </c>
       <c r="B10" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37449-2025 artfynd.xlsx
+++ b/artfynd/A 37449-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181648</v>
       </c>
       <c r="B2" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181660</v>
       </c>
       <c r="B3" t="n">
-        <v>103114</v>
+        <v>103141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181640</v>
       </c>
       <c r="B4" t="n">
-        <v>103128</v>
+        <v>103155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181649</v>
       </c>
       <c r="B5" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181685</v>
       </c>
       <c r="B6" t="n">
-        <v>103114</v>
+        <v>103141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181681</v>
       </c>
       <c r="B7" t="n">
-        <v>98926</v>
+        <v>98953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181705</v>
       </c>
       <c r="B8" t="n">
-        <v>98926</v>
+        <v>98953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181703</v>
       </c>
       <c r="B9" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181687</v>
       </c>
       <c r="B10" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37449-2025 artfynd.xlsx
+++ b/artfynd/A 37449-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181648</v>
       </c>
       <c r="B2" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181660</v>
       </c>
       <c r="B3" t="n">
-        <v>103141</v>
+        <v>103147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181640</v>
       </c>
       <c r="B4" t="n">
-        <v>103155</v>
+        <v>103161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181649</v>
       </c>
       <c r="B5" t="n">
-        <v>100713</v>
+        <v>100719</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181685</v>
       </c>
       <c r="B6" t="n">
-        <v>103141</v>
+        <v>103147</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181681</v>
       </c>
       <c r="B7" t="n">
-        <v>98953</v>
+        <v>98959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181705</v>
       </c>
       <c r="B8" t="n">
-        <v>98953</v>
+        <v>98959</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181703</v>
       </c>
       <c r="B9" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181687</v>
       </c>
       <c r="B10" t="n">
-        <v>100713</v>
+        <v>100719</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37449-2025 artfynd.xlsx
+++ b/artfynd/A 37449-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181648</v>
       </c>
       <c r="B2" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181660</v>
       </c>
       <c r="B3" t="n">
-        <v>103147</v>
+        <v>103154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181640</v>
       </c>
       <c r="B4" t="n">
-        <v>103161</v>
+        <v>103168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181649</v>
       </c>
       <c r="B5" t="n">
-        <v>100719</v>
+        <v>100726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181685</v>
       </c>
       <c r="B6" t="n">
-        <v>103147</v>
+        <v>103154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181681</v>
       </c>
       <c r="B7" t="n">
-        <v>98959</v>
+        <v>98966</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181705</v>
       </c>
       <c r="B8" t="n">
-        <v>98959</v>
+        <v>98966</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181703</v>
       </c>
       <c r="B9" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181687</v>
       </c>
       <c r="B10" t="n">
-        <v>100719</v>
+        <v>100726</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37449-2025 artfynd.xlsx
+++ b/artfynd/A 37449-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181648</v>
       </c>
       <c r="B2" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181660</v>
       </c>
       <c r="B3" t="n">
-        <v>103154</v>
+        <v>103158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181640</v>
       </c>
       <c r="B4" t="n">
-        <v>103168</v>
+        <v>103172</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181649</v>
       </c>
       <c r="B5" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181685</v>
       </c>
       <c r="B6" t="n">
-        <v>103154</v>
+        <v>103158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181681</v>
       </c>
       <c r="B7" t="n">
-        <v>98966</v>
+        <v>98970</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181705</v>
       </c>
       <c r="B8" t="n">
-        <v>98966</v>
+        <v>98970</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181703</v>
       </c>
       <c r="B9" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181687</v>
       </c>
       <c r="B10" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37449-2025 artfynd.xlsx
+++ b/artfynd/A 37449-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181648</v>
       </c>
       <c r="B2" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181660</v>
       </c>
       <c r="B3" t="n">
-        <v>103158</v>
+        <v>103165</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181640</v>
       </c>
       <c r="B4" t="n">
-        <v>103172</v>
+        <v>103179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181649</v>
       </c>
       <c r="B5" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181685</v>
       </c>
       <c r="B6" t="n">
-        <v>103158</v>
+        <v>103165</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181681</v>
       </c>
       <c r="B7" t="n">
-        <v>98970</v>
+        <v>98977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181705</v>
       </c>
       <c r="B8" t="n">
-        <v>98970</v>
+        <v>98977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181703</v>
       </c>
       <c r="B9" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181687</v>
       </c>
       <c r="B10" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37449-2025 artfynd.xlsx
+++ b/artfynd/A 37449-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181648</v>
       </c>
       <c r="B2" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181660</v>
       </c>
       <c r="B3" t="n">
-        <v>103168</v>
+        <v>103173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181640</v>
       </c>
       <c r="B4" t="n">
-        <v>103182</v>
+        <v>103187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181649</v>
       </c>
       <c r="B5" t="n">
-        <v>100740</v>
+        <v>100745</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181685</v>
       </c>
       <c r="B6" t="n">
-        <v>103168</v>
+        <v>103173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181681</v>
       </c>
       <c r="B7" t="n">
-        <v>98980</v>
+        <v>98985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181705</v>
       </c>
       <c r="B8" t="n">
-        <v>98980</v>
+        <v>98985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181703</v>
       </c>
       <c r="B9" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181687</v>
       </c>
       <c r="B10" t="n">
-        <v>100740</v>
+        <v>100745</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37449-2025 artfynd.xlsx
+++ b/artfynd/A 37449-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84181648</v>
       </c>
       <c r="B2" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84181660</v>
       </c>
       <c r="B3" t="n">
-        <v>103173</v>
+        <v>103181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>84181640</v>
       </c>
       <c r="B4" t="n">
-        <v>103187</v>
+        <v>103195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>84181649</v>
       </c>
       <c r="B5" t="n">
-        <v>100745</v>
+        <v>100753</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>84181685</v>
       </c>
       <c r="B6" t="n">
-        <v>103173</v>
+        <v>103181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>84181681</v>
       </c>
       <c r="B7" t="n">
-        <v>98985</v>
+        <v>98993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>84181705</v>
       </c>
       <c r="B8" t="n">
-        <v>98985</v>
+        <v>98993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>84181703</v>
       </c>
       <c r="B9" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>84181687</v>
       </c>
       <c r="B10" t="n">
-        <v>100745</v>
+        <v>100753</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
